--- a/backend/downloads/미분양주택현황보고_공사완료후 미분양현황 (200701 ~ 202508).xlsx
+++ b/backend/downloads/미분양주택현황보고_공사완료후 미분양현황 (200701 ~ 202508).xlsx
@@ -169,7 +169,7 @@
     <row r="2" customHeight="true" ht="25.0">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>다운로드 시간 : 2025-10-14   10:00</t>
+          <t>다운로드 시간 : 2025-10-14   23:55</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">

--- a/backend/downloads/미분양주택현황보고_공사완료후 미분양현황 (200701 ~ 202508).xlsx
+++ b/backend/downloads/미분양주택현황보고_공사완료후 미분양현황 (200701 ~ 202508).xlsx
@@ -169,7 +169,7 @@
     <row r="2" customHeight="true" ht="25.0">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>다운로드 시간 : 2025-10-14   23:55</t>
+          <t>다운로드 시간 : 2025-10-15   10:04</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">

--- a/backend/downloads/미분양주택현황보고_공사완료후 미분양현황 (200701 ~ 202508).xlsx
+++ b/backend/downloads/미분양주택현황보고_공사완료후 미분양현황 (200701 ~ 202508).xlsx
@@ -169,7 +169,7 @@
     <row r="2" customHeight="true" ht="25.0">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>다운로드 시간 : 2025-10-15   10:04</t>
+          <t>다운로드 시간 : 2025-10-17   03:00</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
